--- a/results/Int All Data -0.5/Rando_1_permute.xlsx
+++ b/results/Int All Data -0.5/Rando_1_permute.xlsx
@@ -440,167 +440,167 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.7459769322269865</v>
+        <v>0.7632505198859718</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>accx_n_above_mean</t>
+          <t>accx_skewness</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.7472832195515227</v>
+        <v>0.7632505198859718</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>accy_skewness</t>
+          <t>scl_skewness</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.7415835242820468</v>
+        <v>0.7626188079466161</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>scr_n_sign_changes</t>
+          <t>accz_lineintegral</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.7415835242820468</v>
+        <v>0.7635949514861995</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>scl_peaks</t>
+          <t>accx_max</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.7415835242820468</v>
+        <v>0.7651885191498635</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr_5_95</t>
+          <t>scr_std</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.7459626444117116</v>
+        <v>0.7651742313345886</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>bvp_sum</t>
+          <t>hrv_sum</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.7459626444117116</v>
+        <v>0.7648583753649107</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>accy_max</t>
+          <t>accz_n_below_mean</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.7406058567088341</v>
+        <v>0.7636378149320243</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr</t>
+          <t>bvp_energy</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.7495069751209129</v>
+        <v>0.7686915104468696</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>accz_min</t>
+          <t>hrv_entropy</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.7513020962320555</v>
+        <v>0.7620156716378104</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>hrv_ptp</t>
+          <t>hrv_mean</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.7511862696762266</v>
+        <v>0.7620156716378104</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_5</t>
+          <t>accz_pct_95</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.7515021256459045</v>
+        <v>0.7498131153762039</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>accz_energy</t>
+          <t>accx_n_above_mean</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.7411074542770861</v>
+        <v>0.7491242521757484</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>accz_peaks</t>
+          <t>hrv_ptp</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.7379060311344829</v>
+        <v>0.7523113875030767</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>bvp_mean</t>
+          <t>accz_std</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.7379060311344829</v>
+        <v>0.7545080914755465</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>bvp_ptp</t>
+          <t>scr_lineintegral</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.7377774407970086</v>
+        <v>0.755168379045452</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>hrv_energy</t>
+          <t>accz_n_above_mean</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.7405629932630093</v>
+        <v>0.7529573872577072</v>
       </c>
     </row>
     <row r="19">
@@ -610,1377 +610,1377 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.7434056969901097</v>
+        <v>0.753000250703532</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>bvp_kurtosis</t>
+          <t>hrv_pct_5</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.7380647211361366</v>
+        <v>0.7475449723273593</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>scl_skewness</t>
+          <t>scl_iqr</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.7389408499687955</v>
+        <v>0.7387010051763803</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_95</t>
+          <t>accx_min</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.7360409949805953</v>
+        <v>0.7476021235884591</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>scl_kurtosis</t>
+          <t>scr_n_above_mean</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.7357394268261923</v>
+        <v>0.7450752758310364</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>accy_svd_entropy</t>
+          <t>accy_energy</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.735523585563439</v>
+        <v>0.7453911318007143</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>accz_n_below_mean</t>
+          <t>scr_iqr_5_95</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.7363997143960979</v>
+        <v>0.7428642840432917</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>scl_entropy</t>
+          <t>accx_pct_5</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.7313460188812526</v>
+        <v>0.7653329213362422</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>accy_iqr</t>
+          <t>scl_max</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.7347903348835296</v>
+        <v>0.7600633845586438</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>scr_svd_entropy</t>
+          <t>scl_svd_entropy</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.7382218871041608</v>
+        <v>0.7647440728427113</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>scl_ptp</t>
+          <t>scl_kurtosis</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.7413804468009391</v>
+        <v>0.7653900725973419</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>scr_mean</t>
+          <t>scr_skewness</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.7391408793826444</v>
+        <v>0.767270920600134</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_below_mean</t>
+          <t>scl_lineintegral</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.7391265915673695</v>
+        <v>0.7688073370026982</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>accy_ptp</t>
+          <t>hrv_std</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.739513886613422</v>
+        <v>0.7767751753210186</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>accx_sum</t>
+          <t>accx_perm_entropy</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.7499799970586151</v>
+        <v>0.7791290452615127</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>accz_mean</t>
+          <t>accy_lineintegral</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.7212100522210123</v>
+        <v>0.7781671895372043</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>scr_lineintegral</t>
+          <t>scl_pct_5</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.7243828997330655</v>
+        <v>0.7756260539645068</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_sign_changes</t>
+          <t>accy_rms</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.7243828997330655</v>
+        <v>0.7700263734019555</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>accx_perm_entropy</t>
+          <t>accz_rms</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.7349791245493623</v>
+        <v>0.7696390783559031</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>accz_pct_5</t>
+          <t>scl_std</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.7150087593832846</v>
+        <v>0.769653366171178</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>accz_pct_95</t>
+          <t>bvp_n_below_mean</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.6838119814951837</v>
+        <v>0.7649854416687558</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>hrv_min</t>
+          <t>scr_iqr</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.6850039662975203</v>
+        <v>0.7627458742504611</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>bvp_skewness</t>
+          <t>accz_sum</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.6840992618343116</v>
+        <v>0.708077263932906</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>accz_sum</t>
+          <t>scl_n_above_mean</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.6102394485436716</v>
+        <v>0.7080629761176309</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>bvp_std</t>
+          <t>scr_n_below_mean</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.6064333650586334</v>
+        <v>0.7071154082085975</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>bvp_min</t>
+          <t>bvp_pct_95</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.6113584702360042</v>
+        <v>0.7169926701602598</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>scr_energy</t>
+          <t>bvp_ptp</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.6129520378996683</v>
+        <v>0.7065122718997918</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>bvp_svd_entropy</t>
+          <t>accy_pct_5</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.6110140386357765</v>
+        <v>0.6858959069790833</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>accx_skewness</t>
+          <t>accy_perm_entropy</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.6132536060540712</v>
+        <v>0.6903607540003978</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>scl_lineintegral</t>
+          <t>accx_lineintegral</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.6179914455992386</v>
+        <v>0.6815596502952435</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>scr_min</t>
+          <t>bvp_lineintegral</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.6179914455992386</v>
+        <v>0.6840278227579369</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>hrv_entropy</t>
+          <t>accz_peaks</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.6075125713723999</v>
+        <v>0.6512089015756222</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>hrv_perm_entropy</t>
+          <t>accy_iqr_5_95</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.607211003217997</v>
+        <v>0.6566356043212449</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>accx_std</t>
+          <t>accy_iqr</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.6028334071219615</v>
+        <v>0.6601243078029759</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>bvp_peaks</t>
+          <t>accx_entropy</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.6019715661045777</v>
+        <v>0.6532326277311635</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>accy_n_above_mean</t>
+          <t>accx_iqr</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.6108441088861066</v>
+        <v>0.6570371871825724</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>hrv_rms</t>
+          <t>accz_energy</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.6155390849854493</v>
+        <v>0.6553578926272587</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>accx_max</t>
+          <t>hrv_skewness</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.6113900939338127</v>
+        <v>0.6556737485969366</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>accz_iqr</t>
+          <t>scr_entropy</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.6072411028821763</v>
+        <v>0.6556737485969366</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_sign_changes</t>
+          <t>bvp_rms</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.6161707969248049</v>
+        <v>0.6655367227333238</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr_5_95</t>
+          <t>accy_n_below_mean</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.6162708116317295</v>
+        <v>0.6639145794391099</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>scl_n_sign_changes</t>
+          <t>scr_n_sign_changes</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.6159978191078764</v>
+        <v>0.6639145794391099</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>accx_rms</t>
+          <t>accy_max</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.6181659474497965</v>
+        <v>0.6564912021348663</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>bvp_max</t>
+          <t>accz_max</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.617778652403744</v>
+        <v>0.6288989542843253</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>accy_pct_95</t>
+          <t>hrv_energy</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.6039208051164857</v>
+        <v>0.6323876577660563</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>scl_rms</t>
+          <t>scr_energy</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.6025573665308499</v>
+        <v>0.6378429361422289</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>accx_min</t>
+          <t>bvp_iqr_5_95</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.5969005347071988</v>
+        <v>0.6476773346480663</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>accx_iqr</t>
+          <t>scr_kurtosis</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.5978338148009574</v>
+        <v>0.6476773346480663</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_5</t>
+          <t>accy_entropy</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.5960830811692691</v>
+        <v>0.6450647599989942</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>accz_n_sign_changes</t>
+          <t>accx_kurtosis</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.5888168698330497</v>
+        <v>0.6451361990753688</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>bvp_energy</t>
+          <t>scl_n_below_mean</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.5827870307786212</v>
+        <v>0.6466297520321084</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>hrv_max</t>
+          <t>accz_ptp</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.5699098991318342</v>
+        <v>0.6389634818681909</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_95</t>
+          <t>accx_peaks</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.5591692721291588</v>
+        <v>0.6495581826508583</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>accx_lineintegral</t>
+          <t>accx_iqr_5_95</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.5488761395008943</v>
+        <v>0.6476058955716917</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>scr_skewness</t>
+          <t>bvp_perm_entropy</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.5488761395008943</v>
+        <v>0.6562768849057423</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>accz_entropy</t>
+          <t>accy_pct_95</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.5332879425317398</v>
+        <v>0.6392762897706101</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_above_mean</t>
+          <t>accy_svd_entropy</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.5320245186530286</v>
+        <v>0.6293418765578481</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>bvp_perm_entropy</t>
+          <t>accy_mean</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.5124639280290358</v>
+        <v>0.6290117327728953</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>accx_entropy</t>
+          <t>accz_n_sign_changes</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.5003185230285292</v>
+        <v>0.6216470307633808</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>accz_n_above_mean</t>
+          <t>scl_peaks</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.4945759643132285</v>
+        <v>0.6216470307633808</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>scr_n_below_mean</t>
+          <t>scl_min</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.4964711001312955</v>
+        <v>0.6094143748375952</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>scl_n_above_mean</t>
+          <t>accz_perm_entropy</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.4915791426853625</v>
+        <v>0.5824635546407967</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>accy_lineintegral</t>
+          <t>scr_pct_95</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.5065386757824198</v>
+        <v>0.5761336714655946</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>scl_sum</t>
+          <t>hrv_n_below_mean</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.490977530410186</v>
+        <v>0.5782446485464148</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>scl_svd_entropy</t>
+          <t>scl_iqr_5_95</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.4916378179800915</v>
+        <v>0.5863568890511138</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>scr_kurtosis</t>
+          <t>accy_n_sign_changes</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.4895268408992713</v>
+        <v>0.5908360238877031</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>scl_perm_entropy</t>
+          <t>accz_mean</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.4895411287145462</v>
+        <v>0.5146947322539619</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>accz_max</t>
+          <t>accx_mean</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.4893870108137806</v>
+        <v>0.5061191855259478</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>scr_rms</t>
+          <t>scl_entropy</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.4899758593073115</v>
+        <v>0.5104697300250627</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>accy_pct_5</t>
+          <t>accz_iqr</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.5080270851256603</v>
+        <v>0.5150218279716561</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>hrv_std</t>
+          <t>hrv_iqr</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.5139711972884393</v>
+        <v>0.5206628479464028</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_above_mean</t>
+          <t>accz_kurtosis</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.5353779641501569</v>
+        <v>0.520318416346175</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_95</t>
+          <t>scr_max</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>0.5353779641501569</v>
+        <v>0.5235055516735032</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="1" t="inlineStr">
         <is>
-          <t>accy_iqr_5_95</t>
+          <t>hrv_max</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>0.5228850794821638</v>
+        <v>0.5260421151453128</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="1" t="inlineStr">
         <is>
-          <t>accy_n_below_mean</t>
+          <t>hrv_perm_entropy</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>0.5271641849049041</v>
+        <v>0.5264452220402696</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="1" t="inlineStr">
         <is>
-          <t>accx_iqr_5_95</t>
+          <t>scr_perm_entropy</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>0.5371414615634909</v>
+        <v>0.5261150782553168</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="1" t="inlineStr">
         <is>
-          <t>hrv_peaks</t>
+          <t>bvp_peaks</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>0.5339543262361627</v>
+        <v>0.5195520179348277</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="1" t="inlineStr">
         <is>
-          <t>bvp_entropy</t>
+          <t>scl_mean</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>0.5339543262361627</v>
+        <v>0.5129746697990638</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_5</t>
+          <t>scr_svd_entropy</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>0.5248750863936563</v>
+        <v>0.5115984674317824</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="1" t="inlineStr">
         <is>
-          <t>accx_n_below_mean</t>
+          <t>hrv_peaks</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>0.5330730537900049</v>
+        <v>0.5112968992773794</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="1" t="inlineStr">
         <is>
-          <t>accz_skewness</t>
+          <t>hrv_svd_entropy</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>0.5378537567809971</v>
+        <v>0.5062289159472593</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="1" t="inlineStr">
         <is>
-          <t>accx_peaks</t>
+          <t>bvp_svd_entropy</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>0.5340619611112338</v>
+        <v>0.5131777472801715</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="1" t="inlineStr">
         <is>
-          <t>hrv_mean</t>
+          <t>accz_entropy</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>0.5399315861303795</v>
+        <v>0.520142390461988</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_5</t>
+          <t>scr_rms</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>0.538842664102226</v>
+        <v>0.5202439292025418</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="1" t="inlineStr">
         <is>
-          <t>accx_kurtosis</t>
+          <t>accx_energy</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>0.538842664102226</v>
+        <v>0.526345207333345</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="1" t="inlineStr">
         <is>
-          <t>scr_n_above_mean</t>
+          <t>scr_pct_5</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>0.5415710653071271</v>
+        <v>0.5242102267228629</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="1" t="inlineStr">
         <is>
-          <t>accy_entropy</t>
+          <t>hrv_kurtosis</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>0.5418869212768049</v>
+        <v>0.5248848021080433</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="1" t="inlineStr">
         <is>
-          <t>accz_lineintegral</t>
+          <t>scl_energy</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>0.5055680568647428</v>
+        <v>0.5276718786076734</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="1" t="inlineStr">
         <is>
-          <t>accx_mean</t>
+          <t>bvp_entropy</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>0.5044903745846055</v>
+        <v>0.5276718786076734</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_below_mean</t>
+          <t>accz_skewness</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>0.5003429075665984</v>
+        <v>0.5276718786076734</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr</t>
+          <t>accx_n_below_mean</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>0.5010031951365039</v>
+        <v>0.5267671741444646</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr_5_95</t>
+          <t>bvp_skewness</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>0.4991223471337118</v>
+        <v>0.5160596948732271</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="1" t="inlineStr">
         <is>
-          <t>hrv_sum</t>
+          <t>scl_sum</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>0.4976430819922473</v>
+        <v>0.5228340243555815</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="1" t="inlineStr">
         <is>
-          <t>scl_mean</t>
+          <t>accx_rms</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>0.4959352118063837</v>
+        <v>0.5150963151152893</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="1" t="inlineStr">
         <is>
-          <t>bvp_rms</t>
+          <t>scr_ptp</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>0.4908085531815345</v>
+        <v>0.5100283317851692</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="1" t="inlineStr">
         <is>
-          <t>hrv_svd_entropy</t>
+          <t>hrv_pct_95</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>0.4950162195279001</v>
+        <v>0.5084730554664419</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="1" t="inlineStr">
         <is>
-          <t>hrv_skewness</t>
+          <t>hrv_n_above_mean</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>0.495332075497578</v>
+        <v>0.5094063355602005</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="1" t="inlineStr">
         <is>
-          <t>accx_n_sign_changes</t>
+          <t>hrv_rms</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>0.4981747792246784</v>
+        <v>0.5107983497763862</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_95</t>
+          <t>scl_rms</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>0.4976145063616974</v>
+        <v>0.5127521608891822</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="1" t="inlineStr">
         <is>
-          <t>accy_kurtosis</t>
+          <t>accy_ptp</t>
         </is>
       </c>
       <c r="B118" t="n">
-        <v>0.4976145063616974</v>
+        <v>0.5133568212316173</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="1" t="inlineStr">
         <is>
-          <t>accy_mean</t>
+          <t>hrv_lineintegral</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>0.4942543932174407</v>
+        <v>0.5081985389089595</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="1" t="inlineStr">
         <is>
-          <t>accy_std</t>
+          <t>scl_pct_95</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>0.4868009162490179</v>
+        <v>0.4976053621599215</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="1" t="inlineStr">
         <is>
-          <t>scr_perm_entropy</t>
+          <t>bvp_min</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>0.4890119080367628</v>
+        <v>0.4934119836288308</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="1" t="inlineStr">
         <is>
-          <t>bvp_lineintegral</t>
+          <t>hrv_n_sign_changes</t>
         </is>
       </c>
       <c r="B122" t="n">
-        <v>0.4935925816139059</v>
+        <v>0.4934119836288308</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="1" t="inlineStr">
         <is>
-          <t>scl_std</t>
+          <t>scr_peaks</t>
         </is>
       </c>
       <c r="B123" t="n">
-        <v>0.4925592868132228</v>
+        <v>0.4962577354231898</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="1" t="inlineStr">
         <is>
-          <t>scl_max</t>
+          <t>scl_n_sign_changes</t>
         </is>
       </c>
       <c r="B124" t="n">
-        <v>0.4957607099558259</v>
+        <v>0.4923373494159522</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="1" t="inlineStr">
         <is>
-          <t>accy_min</t>
+          <t>bvp_n_sign_changes</t>
         </is>
       </c>
       <c r="B125" t="n">
-        <v>0.5017476855644296</v>
+        <v>0.4867346207861423</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="1" t="inlineStr">
         <is>
-          <t>scl_energy</t>
+          <t>accy_min</t>
         </is>
       </c>
       <c r="B126" t="n">
-        <v>0.5018619880866291</v>
+        <v>0.486314178008652</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="1" t="inlineStr">
         <is>
-          <t>accz_kurtosis</t>
+          <t>scr_sum</t>
         </is>
       </c>
       <c r="B127" t="n">
-        <v>0.5009429958081455</v>
+        <v>0.4967833365211037</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="1" t="inlineStr">
         <is>
-          <t>accx_svd_entropy</t>
+          <t>accy_std</t>
         </is>
       </c>
       <c r="B128" t="n">
-        <v>0.5000367673113075</v>
+        <v>0.5033269654128187</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr</t>
+          <t>hrv_iqr_5_95</t>
         </is>
       </c>
       <c r="B129" t="n">
-        <v>0.5053649793836351</v>
+        <v>0.5031412238142446</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="1" t="inlineStr">
         <is>
-          <t>hrv_lineintegral</t>
+          <t>accx_std</t>
         </is>
       </c>
       <c r="B130" t="n">
-        <v>0.4993208525139315</v>
+        <v>0.5044347473571352</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="1" t="inlineStr">
         <is>
-          <t>scr_sum</t>
+          <t>accx_n_sign_changes</t>
         </is>
       </c>
       <c r="B131" t="n">
-        <v>0.5041173673538279</v>
+        <v>0.5050378836659409</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="1" t="inlineStr">
         <is>
-          <t>accz_perm_entropy</t>
+          <t>bvp_kurtosis</t>
         </is>
       </c>
       <c r="B132" t="n">
-        <v>0.4801062175237959</v>
+        <v>0.501749209598059</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="1" t="inlineStr">
         <is>
-          <t>scl_min</t>
+          <t>bvp_std</t>
         </is>
       </c>
       <c r="B133" t="n">
-        <v>0.481198187619208</v>
+        <v>0.4998525497463627</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="1" t="inlineStr">
         <is>
-          <t>scr_peaks</t>
+          <t>scl_perm_entropy</t>
         </is>
       </c>
       <c r="B134" t="n">
-        <v>0.481198187619208</v>
+        <v>0.4998525497463627</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="1" t="inlineStr">
         <is>
-          <t>accx_pct_95</t>
+          <t>accy_skewness</t>
         </is>
       </c>
       <c r="B135" t="n">
-        <v>0.4826774527606726</v>
+        <v>0.4998525497463627</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr</t>
+          <t>accz_min</t>
         </is>
       </c>
       <c r="B136" t="n">
-        <v>0.4875183550800232</v>
+        <v>0.5075504436080887</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="1" t="inlineStr">
         <is>
-          <t>accz_rms</t>
+          <t>bvp_max</t>
         </is>
       </c>
       <c r="B137" t="n">
-        <v>0.4964811968540898</v>
+        <v>0.510694715489592</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="1" t="inlineStr">
         <is>
-          <t>accz_iqr_5_95</t>
+          <t>bvp_sum</t>
         </is>
       </c>
       <c r="B138" t="n">
-        <v>0.5003158559696779</v>
+        <v>0.510694715489592</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="1" t="inlineStr">
         <is>
-          <t>accx_pct_5</t>
+          <t>bvp_iqr</t>
         </is>
       </c>
       <c r="B139" t="n">
-        <v>0.5003158559696779</v>
+        <v>0.5176149711919543</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="1" t="inlineStr">
         <is>
-          <t>scr_ptp</t>
+          <t>accy_kurtosis</t>
         </is>
       </c>
       <c r="B140" t="n">
-        <v>0.5003158559696779</v>
+        <v>0.5172848274070015</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="1" t="inlineStr">
         <is>
-          <t>scr_max</t>
+          <t>bvp_n_above_mean</t>
         </is>
       </c>
       <c r="B141" t="n">
-        <v>0.5003158559696779</v>
+        <v>0.507766284870842</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr_5_95</t>
+          <t>accy_n_above_mean</t>
         </is>
       </c>
       <c r="B142" t="n">
-        <v>0.5006317119393556</v>
+        <v>0.5071488607467612</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="1" t="inlineStr">
         <is>
-          <t>accz_svd_entropy</t>
+          <t>accz_pct_5</t>
         </is>
       </c>
       <c r="B143" t="n">
-        <v>0.5009475679090335</v>
+        <v>0.5009460438754042</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="1" t="inlineStr">
         <is>
-          <t>hrv_kurtosis</t>
+          <t>accx_ptp</t>
         </is>
       </c>
       <c r="B144" t="n">
-        <v>0.5009475679090335</v>
+        <v>0.5005730366446266</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="1" t="inlineStr">
         <is>
-          <t>scl_n_below_mean</t>
+          <t>accx_svd_entropy</t>
         </is>
       </c>
       <c r="B145" t="n">
-        <v>0.5009475679090335</v>
+        <v>0.5036744450803051</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="1" t="inlineStr">
         <is>
-          <t>scr_std</t>
+          <t>accx_sum</t>
         </is>
       </c>
       <c r="B146" t="n">
-        <v>0.5006317119393556</v>
+        <v>0.5039331497888833</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="1" t="inlineStr">
         <is>
-          <t>accz_ptp</t>
+          <t>accy_sum</t>
         </is>
       </c>
       <c r="B147" t="n">
-        <v>0.5006317119393556</v>
+        <v>0.5006016122751764</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="1" t="inlineStr">
         <is>
-          <t>accy_perm_entropy</t>
+          <t>bvp_mean</t>
         </is>
       </c>
       <c r="B148" t="n">
-        <v>0.5012634238787113</v>
+        <v>0.5006016122751764</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="1" t="inlineStr">
         <is>
-          <t>accx_energy</t>
+          <t>accz_svd_entropy</t>
         </is>
       </c>
       <c r="B149" t="n">
-        <v>0.5009618557243084</v>
+        <v>0.5048220424031876</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="1" t="inlineStr">
         <is>
-          <t>scr_entropy</t>
+          <t>bvp_pct_5</t>
         </is>
       </c>
       <c r="B150" t="n">
-        <v>0.5009618557243084</v>
+        <v>0.5029396703667663</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="1" t="inlineStr">
         <is>
-          <t>accy_sum</t>
+          <t>scr_mean</t>
         </is>
       </c>
       <c r="B151" t="n">
-        <v>0.5009475679090335</v>
+        <v>0.5024237849832394</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="1" t="inlineStr">
         <is>
-          <t>accx_ptp</t>
+          <t>hrv_min</t>
         </is>
       </c>
       <c r="B152" t="n">
-        <v>0.5009475679090335</v>
+        <v>0.5071886761253274</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="1" t="inlineStr">
         <is>
-          <t>accz_std</t>
+          <t>scl_ptp</t>
         </is>
       </c>
       <c r="B153" t="n">
-        <v>0.5006459997546305</v>
+        <v>0.5068013810792749</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="1" t="inlineStr">
         <is>
-          <t>accy_n_sign_changes</t>
+          <t>accz_iqr_5_95</t>
         </is>
       </c>
       <c r="B154" t="n">
-        <v>0.5006459997546305</v>
+        <v>0.5049047212275786</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="1" t="inlineStr">
         <is>
-          <t>accy_energy</t>
+          <t>accx_pct_95</t>
         </is>
       </c>
       <c r="B155" t="n">
-        <v>0.4997412952914219</v>
+        <v>0.501271615559469</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="1" t="inlineStr">
         <is>
-          <t>accy_rms</t>
+          <t>scr_min</t>
         </is>
       </c>
       <c r="B156" t="n">
-        <v>0.5003158559696779</v>
+        <v>0.501271615559469</v>
       </c>
     </row>
   </sheetData>
